--- a/Util/openl-maven-plugin/it/openl-migrate/rules/Format.xlsx
+++ b/Util/openl-maven-plugin/it/openl-migrate/rules/Format.xlsx
@@ -44,7 +44,7 @@
     <t>Method String day(Date date)</t>
   </si>
   <si>
-    <t>return format(date);</t>
+    <t>return dateToString(date);</t>
   </si>
   <si>
     <t>Test day dayTest</t>
